--- a/artfynd/A 38680-2025 artfynd.xlsx
+++ b/artfynd/A 38680-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74465593</v>
       </c>
       <c r="B2" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575418.4800868529</v>
+        <v>575418</v>
       </c>
       <c r="R2" t="n">
-        <v>6371640.548754885</v>
+        <v>6371641</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 38680-2025 artfynd.xlsx
+++ b/artfynd/A 38680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465593</v>
       </c>
       <c r="B2" t="n">
-        <v>110493</v>
+        <v>110502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38680-2025 artfynd.xlsx
+++ b/artfynd/A 38680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465593</v>
       </c>
       <c r="B2" t="n">
-        <v>110502</v>
+        <v>110507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38680-2025 artfynd.xlsx
+++ b/artfynd/A 38680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465593</v>
       </c>
       <c r="B2" t="n">
-        <v>110507</v>
+        <v>110535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38680-2025 artfynd.xlsx
+++ b/artfynd/A 38680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465593</v>
       </c>
       <c r="B2" t="n">
-        <v>110535</v>
+        <v>110541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38680-2025 artfynd.xlsx
+++ b/artfynd/A 38680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465593</v>
       </c>
       <c r="B2" t="n">
-        <v>110541</v>
+        <v>110548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38680-2025 artfynd.xlsx
+++ b/artfynd/A 38680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465593</v>
       </c>
       <c r="B2" t="n">
-        <v>110548</v>
+        <v>110552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38680-2025 artfynd.xlsx
+++ b/artfynd/A 38680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465593</v>
       </c>
       <c r="B2" t="n">
-        <v>110552</v>
+        <v>110560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38680-2025 artfynd.xlsx
+++ b/artfynd/A 38680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465593</v>
       </c>
       <c r="B2" t="n">
-        <v>110563</v>
+        <v>110568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38680-2025 artfynd.xlsx
+++ b/artfynd/A 38680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465593</v>
       </c>
       <c r="B2" t="n">
-        <v>110568</v>
+        <v>110576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38680-2025 artfynd.xlsx
+++ b/artfynd/A 38680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74465593</v>
       </c>
       <c r="B2" t="n">
-        <v>110576</v>
+        <v>110586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
